--- a/メッセージ仕様書.xlsx
+++ b/メッセージ仕様書.xlsx
@@ -1040,9 +1040,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B8:B11"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B12:B15"/>
     <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B12:B15"/>
-    <mergeCell ref="B2:B4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>認証が必要なエンドポイント（/api/user、書籍の登録・更新・削除）に、トークンなし・無効なトークンでアクセスした</t>
+          <t>認証が必要なエンドポイント（書籍の登録・更新・削除）に、トークンなし・無効なトークンでアクセスした</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/メッセージ仕様書.xlsx
+++ b/メッセージ仕様書.xlsx
@@ -1040,9 +1040,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B8:B11"/>
-    <mergeCell ref="B2:B4"/>
     <mergeCell ref="B12:B15"/>
     <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B2:B4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1741,7 +1741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Google Books API の呼び出しに失敗した</t>
+          <t>Google Books API の呼び出しに失敗した（APIがエラーを返した、または接続できない・タイムアウトした）</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1998,6 +1998,31 @@
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>books/create.blade.php（JavaScript）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>サーバーが error キーのないエラーを返した（ログイン切れの401、想定外の500など）</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>401・500など</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>書籍情報の取得中にエラーが発生しました。（入力欄は変更しない）</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>books/create.blade.php（JavaScript）</t>
         </is>
